--- a/data/nzd0590/nzd0590.xlsx
+++ b/data/nzd0590/nzd0590.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G446"/>
+  <dimension ref="A1:G448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12468,6 +12468,60 @@
         <v>197.33</v>
       </c>
       <c r="G446" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>214.68</v>
+      </c>
+      <c r="C447" t="n">
+        <v>205.7</v>
+      </c>
+      <c r="D447" t="n">
+        <v>233.48</v>
+      </c>
+      <c r="E447" t="n">
+        <v>195.95</v>
+      </c>
+      <c r="F447" t="n">
+        <v>197.98</v>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:43+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>216.17</v>
+      </c>
+      <c r="C448" t="n">
+        <v>205.97</v>
+      </c>
+      <c r="D448" t="n">
+        <v>236.01</v>
+      </c>
+      <c r="E448" t="n">
+        <v>196.45</v>
+      </c>
+      <c r="F448" t="n">
+        <v>198.59</v>
+      </c>
+      <c r="G448" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12484,7 +12538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B527"/>
+  <dimension ref="A1:B530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17757,6 +17811,36 @@
       </c>
       <c r="B527" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -17919,28 +18003,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02571935416842066</v>
+        <v>-0.03170633968987337</v>
       </c>
       <c r="J2" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K2" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00195160926670146</v>
+        <v>0.002955051005631093</v>
       </c>
       <c r="M2" t="n">
-        <v>3.365508030342783</v>
+        <v>3.375724874089536</v>
       </c>
       <c r="N2" t="n">
-        <v>19.92157948929714</v>
+        <v>20.06719739638891</v>
       </c>
       <c r="O2" t="n">
-        <v>4.463359663896373</v>
+        <v>4.479642552301345</v>
       </c>
       <c r="P2" t="n">
-        <v>223.37182473357</v>
+        <v>223.4355761720316</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17991,28 +18075,28 @@
         <v>0.1519</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04428522316631268</v>
+        <v>0.04506051553329182</v>
       </c>
       <c r="J3" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K3" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004437239671330917</v>
+        <v>0.00463427603057831</v>
       </c>
       <c r="M3" t="n">
-        <v>4.033350280083632</v>
+        <v>4.019562624078807</v>
       </c>
       <c r="N3" t="n">
-        <v>25.91303936235237</v>
+        <v>25.80107765086431</v>
       </c>
       <c r="O3" t="n">
-        <v>5.090485179464957</v>
+        <v>5.079476119725764</v>
       </c>
       <c r="P3" t="n">
-        <v>203.7014459449786</v>
+        <v>203.6931902388146</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18063,28 +18147,28 @@
         <v>0.119</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2292351503092374</v>
+        <v>-0.2265496169813253</v>
       </c>
       <c r="J4" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K4" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04524309838048979</v>
+        <v>0.0445864241817755</v>
       </c>
       <c r="M4" t="n">
-        <v>6.358634852935686</v>
+        <v>6.34707108345015</v>
       </c>
       <c r="N4" t="n">
-        <v>65.30520768343203</v>
+        <v>65.06690946901537</v>
       </c>
       <c r="O4" t="n">
-        <v>8.081163757988822</v>
+        <v>8.066406230101196</v>
       </c>
       <c r="P4" t="n">
-        <v>237.6796971209409</v>
+        <v>237.6510997592767</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18135,28 +18219,28 @@
         <v>0.1027</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2347739662789016</v>
+        <v>0.2306436408204623</v>
       </c>
       <c r="J5" t="n">
+        <v>447</v>
+      </c>
+      <c r="K5" t="n">
         <v>445</v>
       </c>
-      <c r="K5" t="n">
-        <v>443</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.07647506751173505</v>
+        <v>0.07443672588259842</v>
       </c>
       <c r="M5" t="n">
-        <v>4.825442727907062</v>
+        <v>4.825016323942771</v>
       </c>
       <c r="N5" t="n">
-        <v>38.95072250382778</v>
+        <v>38.88554695350199</v>
       </c>
       <c r="O5" t="n">
-        <v>6.241051394102421</v>
+        <v>6.235827687925797</v>
       </c>
       <c r="P5" t="n">
-        <v>194.8343723418594</v>
+        <v>194.8785943189985</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18207,28 +18291,28 @@
         <v>0.1945</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08182516267856557</v>
+        <v>0.07407486937534727</v>
       </c>
       <c r="J6" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K6" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01151538048938106</v>
+        <v>0.009433820155901329</v>
       </c>
       <c r="M6" t="n">
-        <v>4.239517628556033</v>
+        <v>4.251429995369517</v>
       </c>
       <c r="N6" t="n">
-        <v>34.00379485899447</v>
+        <v>34.24322569022227</v>
       </c>
       <c r="O6" t="n">
-        <v>5.831277292240052</v>
+        <v>5.85177115839489</v>
       </c>
       <c r="P6" t="n">
-        <v>205.4715818369098</v>
+        <v>205.5540249225161</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18266,7 +18350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G446"/>
+  <dimension ref="A1:G448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34751,6 +34835,80 @@
         </is>
       </c>
     </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>-46.899477698569676,168.13878226804238</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>-46.899808102429894,168.13972084670027</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>-46.89979002102988,168.14036246274605</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>-46.89957304615293,168.14147646360274</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>-46.89908778182474,168.14225038041442</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:43+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>-46.89946518363946,168.13878919713704</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>-46.89980583461236,168.13972210227826</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>-46.89977286344815,168.140340713983</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>-46.899569655366705,168.14147216536966</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>-46.89908364568761,168.14224513556636</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0590/nzd0590.xlsx
+++ b/data/nzd0590/nzd0590.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G448"/>
+  <dimension ref="A1:G451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12524,6 +12524,87 @@
       <c r="G448" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>216.31</v>
+      </c>
+      <c r="C449" t="n">
+        <v>205.52</v>
+      </c>
+      <c r="D449" t="n">
+        <v>233.92</v>
+      </c>
+      <c r="E449" t="n">
+        <v>196.54</v>
+      </c>
+      <c r="F449" t="n">
+        <v>197.66</v>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:27:02+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>217.18</v>
+      </c>
+      <c r="C450" t="n">
+        <v>205.89</v>
+      </c>
+      <c r="D450" t="n">
+        <v>235.62</v>
+      </c>
+      <c r="E450" t="n">
+        <v>197.09</v>
+      </c>
+      <c r="F450" t="n">
+        <v>199.2</v>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>217.18</v>
+      </c>
+      <c r="C451" t="n">
+        <v>205.3</v>
+      </c>
+      <c r="D451" t="n">
+        <v>234.95</v>
+      </c>
+      <c r="E451" t="n">
+        <v>196.13</v>
+      </c>
+      <c r="F451" t="n">
+        <v>198.92</v>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12538,7 +12619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B530"/>
+  <dimension ref="A1:B533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17841,6 +17922,36 @@
       </c>
       <c r="B530" t="n">
         <v>0.41</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
@@ -18003,28 +18114,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03170633968987337</v>
+        <v>-0.0386622369407837</v>
       </c>
       <c r="J2" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="K2" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002955051005631093</v>
+        <v>0.0044004116984242</v>
       </c>
       <c r="M2" t="n">
-        <v>3.375724874089536</v>
+        <v>3.382924800467157</v>
       </c>
       <c r="N2" t="n">
-        <v>20.06719739638891</v>
+        <v>20.14592784151935</v>
       </c>
       <c r="O2" t="n">
-        <v>4.479642552301345</v>
+        <v>4.488421531175448</v>
       </c>
       <c r="P2" t="n">
-        <v>223.4355761720316</v>
+        <v>223.5099401439447</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18075,28 +18186,28 @@
         <v>0.1519</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04506051553329182</v>
+        <v>0.04586249170163094</v>
       </c>
       <c r="J3" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="K3" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00463427603057831</v>
+        <v>0.004864433272610102</v>
       </c>
       <c r="M3" t="n">
-        <v>4.019562624078807</v>
+        <v>3.997107758804499</v>
       </c>
       <c r="N3" t="n">
-        <v>25.80107765086431</v>
+        <v>25.63227835094072</v>
       </c>
       <c r="O3" t="n">
-        <v>5.079476119725764</v>
+        <v>5.062833036052119</v>
       </c>
       <c r="P3" t="n">
-        <v>203.6931902388146</v>
+        <v>203.6846171925416</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18147,28 +18258,28 @@
         <v>0.119</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2265496169813253</v>
+        <v>-0.2224970003768031</v>
       </c>
       <c r="J4" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="K4" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0445864241817755</v>
+        <v>0.04358698958675578</v>
       </c>
       <c r="M4" t="n">
-        <v>6.34707108345015</v>
+        <v>6.330237208713696</v>
       </c>
       <c r="N4" t="n">
-        <v>65.06690946901537</v>
+        <v>64.70812883119764</v>
       </c>
       <c r="O4" t="n">
-        <v>8.066406230101196</v>
+        <v>8.044136301132498</v>
       </c>
       <c r="P4" t="n">
-        <v>237.6510997592767</v>
+        <v>237.6077670967519</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18219,28 +18330,28 @@
         <v>0.1027</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2306436408204623</v>
+        <v>0.225060011538231</v>
       </c>
       <c r="J5" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="K5" t="n">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07443672588259842</v>
+        <v>0.07179684185694202</v>
       </c>
       <c r="M5" t="n">
-        <v>4.825016323942771</v>
+        <v>4.821167007147216</v>
       </c>
       <c r="N5" t="n">
-        <v>38.88554695350199</v>
+        <v>38.76122396272832</v>
       </c>
       <c r="O5" t="n">
-        <v>6.235827687925797</v>
+        <v>6.225851264102631</v>
       </c>
       <c r="P5" t="n">
-        <v>194.8785943189985</v>
+        <v>194.9386190521187</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18291,28 +18402,28 @@
         <v>0.1945</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07407486937534727</v>
+        <v>0.06311805374304401</v>
       </c>
       <c r="J6" t="n">
+        <v>450</v>
+      </c>
+      <c r="K6" t="n">
         <v>447</v>
       </c>
-      <c r="K6" t="n">
-        <v>444</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.009433820155901329</v>
+        <v>0.006853526421877976</v>
       </c>
       <c r="M6" t="n">
-        <v>4.251429995369517</v>
+        <v>4.267156521738799</v>
       </c>
       <c r="N6" t="n">
-        <v>34.24322569022227</v>
+        <v>34.54487270841881</v>
       </c>
       <c r="O6" t="n">
-        <v>5.85177115839489</v>
+        <v>5.877488639582284</v>
       </c>
       <c r="P6" t="n">
-        <v>205.5540249225161</v>
+        <v>205.6710466992898</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18350,7 +18461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G448"/>
+  <dimension ref="A1:G451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34909,6 +35020,117 @@
         </is>
       </c>
     </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:27:10+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>-46.899464007739944,168.13878984819274</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>-46.89980961430825,168.13972000964827</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>-46.89978703710289,168.1403586803515</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>-46.89956904502517,168.14147139168776</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>-46.89908995160151,168.1422531318105</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:27:02+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>-46.8994567003643,168.13879389403817</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>-46.89980650655831,168.13972173025516</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>-46.89977550829299,168.14034406655824</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>-46.899565315160125,168.14146666363212</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>-46.89907950955026,168.14223989071908</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>-46.8994567003643,168.13879389403817</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>-46.89981146215956,168.13971898658457</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>-46.899780052000615,168.1403498261113</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>-46.899571825469906,168.14147491623876</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>-46.899081408105125,168.14224229818987</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0590/nzd0590.xlsx
+++ b/data/nzd0590/nzd0590.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G451"/>
+  <dimension ref="A1:G453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12605,6 +12605,60 @@
       <c r="G451" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>216.99</v>
+      </c>
+      <c r="C452" t="n">
+        <v>202.85</v>
+      </c>
+      <c r="D452" t="n">
+        <v>233.98</v>
+      </c>
+      <c r="E452" t="n">
+        <v>194.51</v>
+      </c>
+      <c r="F452" t="n">
+        <v>197.48</v>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:21:16+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>216.76</v>
+      </c>
+      <c r="C453" t="n">
+        <v>202.52</v>
+      </c>
+      <c r="D453" t="n">
+        <v>232.59</v>
+      </c>
+      <c r="E453" t="n">
+        <v>195.27</v>
+      </c>
+      <c r="F453" t="n">
+        <v>198.07</v>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12619,7 +12673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B533"/>
+  <dimension ref="A1:B535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17952,6 +18006,26 @@
       </c>
       <c r="B533" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>-0.77</v>
       </c>
     </row>
   </sheetData>
@@ -18114,28 +18188,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0386622369407837</v>
+        <v>-0.04319756382686456</v>
       </c>
       <c r="J2" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K2" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0044004116984242</v>
+        <v>0.005499633606986243</v>
       </c>
       <c r="M2" t="n">
-        <v>3.382924800467157</v>
+        <v>3.387629805942586</v>
       </c>
       <c r="N2" t="n">
-        <v>20.14592784151935</v>
+        <v>20.19286162756129</v>
       </c>
       <c r="O2" t="n">
-        <v>4.488421531175448</v>
+        <v>4.493646807166902</v>
       </c>
       <c r="P2" t="n">
-        <v>223.5099401439447</v>
+        <v>223.5586763353852</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18186,28 +18260,28 @@
         <v>0.1519</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04586249170163094</v>
+        <v>0.04403796837117078</v>
       </c>
       <c r="J3" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K3" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004864433272610102</v>
+        <v>0.004523307969679036</v>
       </c>
       <c r="M3" t="n">
-        <v>3.997107758804499</v>
+        <v>3.989294823733569</v>
       </c>
       <c r="N3" t="n">
-        <v>25.63227835094072</v>
+        <v>25.54098591827164</v>
       </c>
       <c r="O3" t="n">
-        <v>5.062833036052119</v>
+        <v>5.053809050436278</v>
       </c>
       <c r="P3" t="n">
-        <v>203.6846171925416</v>
+        <v>203.7042244425426</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18258,28 +18332,28 @@
         <v>0.119</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2224970003768031</v>
+        <v>-0.2210981870459694</v>
       </c>
       <c r="J4" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K4" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04358698958675578</v>
+        <v>0.04342722353898065</v>
       </c>
       <c r="M4" t="n">
-        <v>6.330237208713696</v>
+        <v>6.311065509556798</v>
       </c>
       <c r="N4" t="n">
-        <v>64.70812883119764</v>
+        <v>64.43687713623117</v>
       </c>
       <c r="O4" t="n">
-        <v>8.044136301132498</v>
+        <v>8.027258382301593</v>
       </c>
       <c r="P4" t="n">
-        <v>237.6077670967519</v>
+        <v>237.5927423714167</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18330,28 +18404,28 @@
         <v>0.1027</v>
       </c>
       <c r="I5" t="n">
-        <v>0.225060011538231</v>
+        <v>0.2200197621315788</v>
       </c>
       <c r="J5" t="n">
+        <v>452</v>
+      </c>
+      <c r="K5" t="n">
         <v>450</v>
       </c>
-      <c r="K5" t="n">
-        <v>448</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.07179684185694202</v>
+        <v>0.06913796094978419</v>
       </c>
       <c r="M5" t="n">
-        <v>4.821167007147216</v>
+        <v>4.825125992593005</v>
       </c>
       <c r="N5" t="n">
-        <v>38.76122396272832</v>
+        <v>38.75621158611175</v>
       </c>
       <c r="O5" t="n">
-        <v>6.225851264102631</v>
+        <v>6.225448705604419</v>
       </c>
       <c r="P5" t="n">
-        <v>194.9386190521187</v>
+        <v>194.9930712585599</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18402,28 +18476,28 @@
         <v>0.1945</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06311805374304401</v>
+        <v>0.05531221580302215</v>
       </c>
       <c r="J6" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K6" t="n">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006853526421877976</v>
+        <v>0.005257089100492718</v>
       </c>
       <c r="M6" t="n">
-        <v>4.267156521738799</v>
+        <v>4.279756537255055</v>
       </c>
       <c r="N6" t="n">
-        <v>34.54487270841881</v>
+        <v>34.79738706636601</v>
       </c>
       <c r="O6" t="n">
-        <v>5.877488639582284</v>
+        <v>5.898931010476899</v>
       </c>
       <c r="P6" t="n">
-        <v>205.6710466992898</v>
+        <v>205.754844655115</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18461,7 +18535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G451"/>
+  <dimension ref="A1:G453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35131,6 +35205,80 @@
         </is>
       </c>
     </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>-46.89945829622796,168.13879301046285</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>-46.899832040502794,168.13970759337047</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>-46.89978663020374,168.14035816457044</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>-46.89958281161646,168.14148884251702</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>-46.899091172100924,168.14225467947082</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:21:16+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>-46.899460228062914,168.13879194087156</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>-46.89983481227951,168.13970605877358</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>-46.89979605670007,168.14037011349998</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>-46.89957765762196,168.1414823092006</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>-46.89908717157501,168.14224960658433</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
